--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -170,24 +170,24 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -203,28 +203,34 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>NIETO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
   </si>
   <si>
     <t>HUERTA</t>
@@ -233,22 +239,19 @@
     <t>VAS</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>SALMERON</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>ANGEL OSWALDO</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>MARTIN ERNESTO</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -257,22 +260,7 @@
     <t>ROSMELY LEILANI</t>
   </si>
   <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>ANGEL OSWALDO</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
     <t>KIMBERLY ALISON</t>
-  </si>
-  <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>MELANI YOSELIN</t>
   </si>
 </sst>
 </file>
@@ -818,28 +806,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -869,10 +857,10 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -884,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -919,28 +907,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -973,19 +961,19 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>7</v>
       </c>
       <c r="AF5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1020,28 +1008,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1080,7 +1068,7 @@
         <v>5</v>
       </c>
       <c r="AD6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>10</v>
@@ -1121,28 +1109,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1169,25 +1157,25 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE7">
         <v>10</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1222,28 +1210,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1276,16 +1264,16 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1323,28 +1311,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1371,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>10</v>
@@ -1383,13 +1371,13 @@
         <v>6</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1424,28 +1412,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1487,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF10">
         <v>5</v>
@@ -1525,28 +1513,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1579,7 +1567,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1591,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1626,28 +1614,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1677,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>6</v>
@@ -1727,28 +1715,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1778,10 +1766,10 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1793,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1828,28 +1816,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1879,10 +1867,10 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1894,7 +1882,7 @@
         <v>6</v>
       </c>
       <c r="AF14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1929,28 +1917,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1977,13 +1965,13 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1995,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="AF15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2030,28 +2018,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2078,25 +2066,25 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>6</v>
       </c>
       <c r="AD16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE16">
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2131,28 +2119,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2182,7 +2170,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2191,10 +2179,10 @@
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2232,28 +2220,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2283,10 +2271,10 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2295,10 +2283,10 @@
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2333,28 +2321,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2384,19 +2372,19 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -2434,28 +2422,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2497,7 +2485,7 @@
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>5</v>
@@ -2535,28 +2523,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2583,13 +2571,13 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2601,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2636,28 +2624,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2684,13 +2672,13 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2737,28 +2725,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2788,16 +2776,16 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
       </c>
       <c r="AD23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE23">
         <v>7</v>
@@ -2838,28 +2826,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2886,19 +2874,19 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>5</v>
       </c>
       <c r="AD24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE24">
         <v>7</v>
@@ -2939,28 +2927,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2987,7 +2975,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -3005,7 +2993,7 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3040,28 +3028,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3094,7 +3082,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -3106,7 +3094,7 @@
         <v>7</v>
       </c>
       <c r="AF26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3275,7 +3263,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3299,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3358,7 +3346,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M5">
         <v>87.5</v>
@@ -3367,7 +3355,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3382,7 +3370,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U5">
         <v>87.5</v>
@@ -3391,7 +3379,7 @@
         <v>100</v>
       </c>
       <c r="W5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -3435,7 +3423,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3444,7 +3432,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3459,7 +3447,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3468,7 +3456,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -3512,7 +3500,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3536,7 +3524,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3583,13 +3571,13 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M8">
         <v>87.5</v>
@@ -3598,22 +3586,22 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>68.8</v>
+        <v>81.3</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U8">
         <v>87.5</v>
@@ -3622,10 +3610,10 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>68.8</v>
+        <v>81.3</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -3660,13 +3648,13 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3675,7 +3663,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3684,13 +3672,13 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3699,7 +3687,7 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -3743,7 +3731,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M10">
         <v>87.5</v>
@@ -3755,7 +3743,7 @@
         <v>68.8</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3767,7 +3755,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U10">
         <v>87.5</v>
@@ -3779,7 +3767,7 @@
         <v>68.8</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -3820,7 +3808,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M11">
         <v>87.5</v>
@@ -3829,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3844,7 +3832,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U11">
         <v>87.5</v>
@@ -3853,7 +3841,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -3891,13 +3879,13 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M12">
         <v>81.3</v>
@@ -3906,7 +3894,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3915,13 +3903,13 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U12">
         <v>81.3</v>
@@ -3930,7 +3918,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -3968,13 +3956,13 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M13">
         <v>87.5</v>
@@ -3983,7 +3971,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3992,13 +3980,13 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="S13">
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U13">
         <v>87.5</v>
@@ -4007,7 +3995,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -4045,19 +4033,19 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O14">
         <v>87.5</v>
@@ -4069,19 +4057,19 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W14">
         <v>87.5</v>
@@ -4128,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -4152,7 +4140,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4205,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4214,7 +4202,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4229,7 +4217,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4238,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X16">
         <v>100</v>
@@ -4282,16 +4270,16 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M17">
         <v>87.5</v>
       </c>
       <c r="N17">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="O17">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4306,16 +4294,16 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U17">
         <v>87.5</v>
       </c>
       <c r="V17">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="W17">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -4359,16 +4347,16 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M18">
         <v>87.5</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O18">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4383,16 +4371,16 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U18">
         <v>87.5</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W18">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="X18">
         <v>100</v>
@@ -4430,19 +4418,19 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M19">
         <v>81.3</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O19">
         <v>81.3</v>
@@ -4454,19 +4442,19 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U19">
         <v>81.3</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W19">
         <v>81.3</v>
@@ -4507,19 +4495,19 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M20">
         <v>81.3</v>
       </c>
       <c r="N20">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="O20">
         <v>93.8</v>
@@ -4531,19 +4519,19 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U20">
         <v>81.3</v>
       </c>
       <c r="V20">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="W20">
         <v>93.8</v>
@@ -4584,13 +4572,13 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M21">
         <v>81.3</v>
@@ -4599,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4608,13 +4596,13 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U21">
         <v>81.3</v>
@@ -4623,7 +4611,7 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X21">
         <v>100</v>
@@ -4661,7 +4649,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4685,7 +4673,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4744,7 +4732,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4753,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4768,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -4777,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -4821,13 +4809,13 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O24">
         <v>93.8</v>
@@ -4845,13 +4833,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W24">
         <v>93.8</v>
@@ -4898,7 +4886,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4907,7 +4895,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4922,7 +4910,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -4931,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="X25">
         <v>100</v>
@@ -4984,7 +4972,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5008,7 +4996,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -5103,7 +5091,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -5112,19 +5100,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>47.8</v>
+        <v>43.5</v>
       </c>
       <c r="G3" s="2">
-        <v>52.2</v>
+        <v>56.5</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5156,7 +5144,7 @@
         <v>52.2</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5167,7 +5155,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -5176,19 +5164,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>69.59999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="G5" s="2">
-        <v>30.4</v>
+        <v>47.8</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5208,19 +5196,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>78.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5231,7 +5219,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -5240,19 +5228,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>78.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5263,7 +5251,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
@@ -5272,19 +5260,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5366,7 +5354,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5398,22 +5386,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920279</v>
+        <v>24330051920256</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5421,19 +5409,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920279</v>
+        <v>24330051920256</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
@@ -5444,22 +5432,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920265</v>
+        <v>24330051920266</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5467,22 +5455,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920265</v>
+        <v>24330051920266</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5490,16 +5478,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920255</v>
+        <v>24330051920257</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5513,22 +5501,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920255</v>
+        <v>24330051920257</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5536,16 +5524,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920266</v>
+        <v>24330051920270</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -5559,22 +5547,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920266</v>
+        <v>24330051920270</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5582,22 +5570,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920270</v>
+        <v>24330051920279</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5605,22 +5593,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920270</v>
+        <v>24330051920265</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5631,13 +5619,13 @@
         <v>24330051920311</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5646,52 +5634,6 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920262</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920368</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -167,12 +167,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -185,7 +185,7 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -212,36 +212,33 @@
     <t>PAZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SALMERON</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>VAS</t>
-  </si>
-  <si>
-    <t>SALMERON</t>
-  </si>
-  <si>
     <t>IRVING JESUS</t>
   </si>
   <si>
@@ -251,16 +248,13 @@
     <t>ALEXIS GABRIEL</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALISON</t>
+  </si>
+  <si>
     <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ROSMELY LEILANI</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALISON</t>
   </si>
 </sst>
 </file>
@@ -815,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>9</v>
@@ -863,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD4">
         <v>9</v>
@@ -916,7 +910,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>8</v>
@@ -1017,7 +1011,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1118,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>10</v>
@@ -1219,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>8</v>
@@ -1320,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>9</v>
@@ -1368,7 +1362,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>8</v>
@@ -1421,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -1522,7 +1516,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>7</v>
@@ -1570,7 +1564,7 @@
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1623,7 +1617,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>8</v>
@@ -1671,7 +1665,7 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD12">
         <v>8</v>
@@ -1724,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>8</v>
@@ -1825,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>8</v>
@@ -1926,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>8</v>
@@ -2027,7 +2021,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>8</v>
@@ -2075,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16">
         <v>8</v>
@@ -2128,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2229,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -2330,7 +2324,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -2431,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -2532,7 +2526,7 @@
         <v>4</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>8</v>
@@ -2633,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>10</v>
@@ -2681,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>10</v>
@@ -2734,7 +2728,7 @@
         <v>4</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>8</v>
@@ -2835,7 +2829,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>9</v>
@@ -2883,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD24">
         <v>9</v>
@@ -2936,7 +2930,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>8</v>
@@ -3037,7 +3031,7 @@
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>9</v>
@@ -3085,7 +3079,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD26">
         <v>10</v>
@@ -3734,7 +3728,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="M10">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3758,7 +3752,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="U10">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3811,7 +3805,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="M11">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3835,7 +3829,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="U11">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3888,7 +3882,7 @@
         <v>93.2</v>
       </c>
       <c r="M12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -3912,7 +3906,7 @@
         <v>93.2</v>
       </c>
       <c r="U12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4042,7 +4036,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N14">
         <v>95.2</v>
@@ -4066,7 +4060,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
         <v>95.2</v>
@@ -4350,7 +4344,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="M18">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="N18">
         <v>95.2</v>
@@ -4374,7 +4368,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="U18">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="V18">
         <v>95.2</v>
@@ -4427,7 +4421,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="M19">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N19">
         <v>95.2</v>
@@ -4451,7 +4445,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="U19">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V19">
         <v>95.2</v>
@@ -4504,7 +4498,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="M20">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N20">
         <v>90.5</v>
@@ -4528,7 +4522,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="U20">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V20">
         <v>90.5</v>
@@ -4581,7 +4575,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="M21">
-        <v>81.3</v>
+        <v>75</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4605,7 +4599,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="U21">
-        <v>81.3</v>
+        <v>75</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4735,7 +4729,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4759,7 +4753,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4966,7 +4960,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4990,7 +4984,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5059,7 +5053,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -5068,19 +5062,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>34.8</v>
+        <v>43.5</v>
       </c>
       <c r="G2" s="2">
-        <v>65.2</v>
+        <v>56.5</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5091,7 +5085,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -5112,7 +5106,7 @@
         <v>56.5</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5354,7 +5348,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5392,10 +5386,10 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5415,10 +5409,10 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -5438,16 +5432,16 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5461,16 +5455,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5484,10 +5478,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5507,16 +5501,16 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5524,7 +5518,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920270</v>
+        <v>24330051920279</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -5533,10 +5527,10 @@
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
@@ -5547,22 +5541,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920270</v>
+        <v>24330051920311</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5570,70 +5564,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920279</v>
+        <v>24330051920270</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920265</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920311</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -56,117 +56,117 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>CARRERA ROSETE ANA MARIA</t>
+  </si>
+  <si>
+    <t>CLEMENTE JUAREZ BRYAN</t>
+  </si>
+  <si>
+    <t>CORTEZ CHACON GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>COTLAME SANCHEZ LUIS MIGUEL</t>
+  </si>
+  <si>
+    <t>FRANCO MARTINEZ LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>GUTIERREZ HUERTA DIEGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ ALVAREZ JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ VAS ROSMELY LEILANI</t>
+  </si>
+  <si>
+    <t>LOPEZ CAMACHO IRVING JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ ROSAS ERNESTO</t>
+  </si>
+  <si>
+    <t>MOTA PALACIOS ANGEL OSWALDO</t>
+  </si>
+  <si>
+    <t>NIETO SALMERON KIMBERLY ALISON</t>
+  </si>
+  <si>
+    <t>PAZ HERNANDEZ ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>RAMOS GONZALEZ SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>ROSAS PANIAGUA RUBEN</t>
+  </si>
+  <si>
+    <t>SANCHEZ HERNANDEZ MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>SANCHEZ NIETO JESUS DAMIAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ PORRAS HEIDI ABRIL</t>
+  </si>
+  <si>
+    <t>TENORIO MARTINEZ MELANI YOSELIN</t>
+  </si>
+  <si>
+    <t>TORRES GUTIERREZ JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>TORRES ROSALES MARTIN ERNESTO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA HERNANDEZ DIANA YURIDIA</t>
+  </si>
+  <si>
+    <t>ZOQUITECATL SANCHEZ LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Aprobados</t>
+  </si>
+  <si>
+    <t>Reprobados</t>
+  </si>
+  <si>
+    <t>Por_Apro</t>
+  </si>
+  <si>
+    <t>Por_Repro</t>
+  </si>
+  <si>
+    <t>Promedio</t>
+  </si>
+  <si>
+    <t>Blancos</t>
+  </si>
+  <si>
+    <t>Por_Blancos</t>
+  </si>
+  <si>
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>CARRERA ROSETE ANA MARIA</t>
-  </si>
-  <si>
-    <t>CLEMENTE JUAREZ BRYAN</t>
-  </si>
-  <si>
-    <t>CORTEZ CHACON GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>COTLAME SANCHEZ LUIS MIGUEL</t>
-  </si>
-  <si>
-    <t>FRANCO MARTINEZ LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>GUTIERREZ HUERTA DIEGO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ ALVAREZ JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ VAS ROSMELY LEILANI</t>
-  </si>
-  <si>
-    <t>LOPEZ CAMACHO IRVING JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ ROSAS ERNESTO</t>
-  </si>
-  <si>
-    <t>MOTA PALACIOS ANGEL OSWALDO</t>
-  </si>
-  <si>
-    <t>NIETO SALMERON KIMBERLY ALISON</t>
-  </si>
-  <si>
-    <t>PAZ HERNANDEZ ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>RAMOS GONZALEZ SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>ROSAS PANIAGUA RUBEN</t>
-  </si>
-  <si>
-    <t>SANCHEZ HERNANDEZ MARBELY YOSELIN</t>
-  </si>
-  <si>
-    <t>SANCHEZ NIETO JESUS DAMIAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ PORRAS HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>TENORIO MARTINEZ MELANI YOSELIN</t>
-  </si>
-  <si>
-    <t>TORRES GUTIERREZ JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>TORRES ROSALES MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA HERNANDEZ DIANA YURIDIA</t>
-  </si>
-  <si>
-    <t>ZOQUITECATL SANCHEZ LUIS ANTONIO</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>Docente</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Aprobados</t>
-  </si>
-  <si>
-    <t>Reprobados</t>
-  </si>
-  <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Blancos</t>
-  </si>
-  <si>
-    <t>Por_Blancos</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -188,7 +188,7 @@
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Faltante Faltante Faltante</t>
   </si>
   <si>
     <t>NC</t>
@@ -616,13 +616,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -633,39 +633,35 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="W1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-    </row>
-    <row r="2" spans="1:33">
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,190 +687,166 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>8</v>
+      </c>
+      <c r="L4">
         <v>10</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33">
-      <c r="A4" s="1" t="s">
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="N4">
+        <v>8</v>
+      </c>
+      <c r="O4">
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <v>-1</v>
+      </c>
+      <c r="Q4">
+        <v>-1</v>
+      </c>
+      <c r="R4">
+        <v>-1</v>
+      </c>
+      <c r="S4">
+        <v>-1</v>
+      </c>
+      <c r="T4">
+        <v>-1</v>
+      </c>
+      <c r="U4">
+        <v>-1</v>
+      </c>
+      <c r="V4">
+        <v>-1</v>
+      </c>
+      <c r="W4">
+        <v>8</v>
+      </c>
+      <c r="X4">
+        <v>9</v>
+      </c>
+      <c r="Y4">
+        <v>8</v>
+      </c>
+      <c r="Z4">
+        <v>9</v>
+      </c>
+      <c r="AA4">
+        <v>9</v>
+      </c>
+      <c r="AB4">
+        <v>9</v>
+      </c>
+      <c r="AC4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>7</v>
-      </c>
-      <c r="K4">
-        <v>9</v>
-      </c>
-      <c r="L4">
-        <v>8</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
-        <v>9</v>
-      </c>
-      <c r="O4">
-        <v>8</v>
-      </c>
-      <c r="P4">
-        <v>8</v>
-      </c>
-      <c r="Q4">
-        <v>10</v>
-      </c>
-      <c r="R4">
-        <v>-1</v>
-      </c>
-      <c r="S4">
-        <v>-1</v>
-      </c>
-      <c r="T4">
-        <v>-1</v>
-      </c>
-      <c r="U4">
-        <v>-1</v>
-      </c>
-      <c r="V4">
-        <v>-1</v>
-      </c>
-      <c r="W4">
-        <v>-1</v>
-      </c>
-      <c r="X4">
-        <v>-1</v>
-      </c>
-      <c r="Y4">
-        <v>-1</v>
-      </c>
-      <c r="Z4">
-        <v>8</v>
-      </c>
-      <c r="AA4">
-        <v>9</v>
-      </c>
-      <c r="AB4">
-        <v>8</v>
-      </c>
-      <c r="AC4">
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <v>9</v>
-      </c>
-      <c r="AE4">
-        <v>9</v>
-      </c>
-      <c r="AF4">
-        <v>7</v>
-      </c>
-      <c r="AG4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -898,31 +870,31 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Q5">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -940,42 +912,30 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>5</v>
-      </c>
-      <c r="AD5">
-        <v>7</v>
-      </c>
-      <c r="AE5">
-        <v>7</v>
-      </c>
-      <c r="AF5">
-        <v>7</v>
-      </c>
-      <c r="AG5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -999,84 +959,72 @@
         <v>5</v>
       </c>
       <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
+        <v>-1</v>
+      </c>
+      <c r="Q6">
+        <v>-1</v>
+      </c>
+      <c r="R6">
+        <v>-1</v>
+      </c>
+      <c r="S6">
+        <v>-1</v>
+      </c>
+      <c r="T6">
+        <v>-1</v>
+      </c>
+      <c r="U6">
+        <v>-1</v>
+      </c>
+      <c r="V6">
+        <v>-1</v>
+      </c>
+      <c r="W6">
+        <v>5</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>5</v>
+      </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
+      <c r="AA6">
+        <v>6</v>
+      </c>
+      <c r="AB6">
         <v>10</v>
       </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6">
-        <v>7</v>
-      </c>
-      <c r="O6">
-        <v>9</v>
-      </c>
-      <c r="P6">
-        <v>6</v>
-      </c>
-      <c r="Q6">
-        <v>10</v>
-      </c>
-      <c r="R6">
-        <v>-1</v>
-      </c>
-      <c r="S6">
-        <v>-1</v>
-      </c>
-      <c r="T6">
-        <v>-1</v>
-      </c>
-      <c r="U6">
-        <v>-1</v>
-      </c>
-      <c r="V6">
-        <v>-1</v>
-      </c>
-      <c r="W6">
-        <v>-1</v>
-      </c>
-      <c r="X6">
-        <v>-1</v>
-      </c>
-      <c r="Y6">
-        <v>-1</v>
-      </c>
-      <c r="Z6">
-        <v>5</v>
-      </c>
-      <c r="AA6">
-        <v>8</v>
-      </c>
-      <c r="AB6">
-        <v>5</v>
-      </c>
       <c r="AC6">
         <v>5</v>
       </c>
-      <c r="AD6">
-        <v>6</v>
-      </c>
-      <c r="AE6">
-        <v>10</v>
-      </c>
-      <c r="AF6">
-        <v>5</v>
-      </c>
-      <c r="AG6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33">
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -1100,84 +1048,72 @@
         <v>6</v>
       </c>
       <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>10</v>
       </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
       <c r="N7">
+        <v>9</v>
+      </c>
+      <c r="O7">
+        <v>9</v>
+      </c>
+      <c r="P7">
+        <v>-1</v>
+      </c>
+      <c r="Q7">
+        <v>-1</v>
+      </c>
+      <c r="R7">
+        <v>-1</v>
+      </c>
+      <c r="S7">
+        <v>-1</v>
+      </c>
+      <c r="T7">
+        <v>-1</v>
+      </c>
+      <c r="U7">
+        <v>-1</v>
+      </c>
+      <c r="V7">
+        <v>-1</v>
+      </c>
+      <c r="W7">
+        <v>9</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>8</v>
+      </c>
+      <c r="Z7">
+        <v>8</v>
+      </c>
+      <c r="AA7">
         <v>10</v>
       </c>
-      <c r="O7">
-        <v>9</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
+      <c r="AB7">
         <v>10</v>
       </c>
-      <c r="R7">
-        <v>-1</v>
-      </c>
-      <c r="S7">
-        <v>-1</v>
-      </c>
-      <c r="T7">
-        <v>-1</v>
-      </c>
-      <c r="U7">
-        <v>-1</v>
-      </c>
-      <c r="V7">
-        <v>-1</v>
-      </c>
-      <c r="W7">
-        <v>-1</v>
-      </c>
-      <c r="X7">
-        <v>-1</v>
-      </c>
-      <c r="Y7">
-        <v>-1</v>
-      </c>
-      <c r="Z7">
-        <v>9</v>
-      </c>
-      <c r="AA7">
-        <v>8</v>
-      </c>
-      <c r="AB7">
-        <v>8</v>
-      </c>
       <c r="AC7">
         <v>8</v>
       </c>
-      <c r="AD7">
-        <v>10</v>
-      </c>
-      <c r="AE7">
-        <v>10</v>
-      </c>
-      <c r="AF7">
-        <v>8</v>
-      </c>
-      <c r="AG7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33">
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -1201,31 +1137,31 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q8">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1243,42 +1179,30 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>5</v>
       </c>
-      <c r="AD8">
-        <v>7</v>
-      </c>
-      <c r="AE8">
-        <v>6</v>
-      </c>
-      <c r="AF8">
-        <v>5</v>
-      </c>
-      <c r="AG8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33">
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1302,84 +1226,72 @@
         <v>7</v>
       </c>
       <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
         <v>10</v>
       </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
       <c r="K9">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <v>9</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>8</v>
+      </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>-1</v>
+      </c>
+      <c r="Q9">
+        <v>-1</v>
+      </c>
+      <c r="R9">
+        <v>-1</v>
+      </c>
+      <c r="S9">
+        <v>-1</v>
+      </c>
+      <c r="T9">
+        <v>-1</v>
+      </c>
+      <c r="U9">
+        <v>-1</v>
+      </c>
+      <c r="V9">
+        <v>-1</v>
+      </c>
+      <c r="W9">
+        <v>7</v>
+      </c>
+      <c r="X9">
         <v>10</v>
       </c>
-      <c r="L9">
-        <v>5</v>
-      </c>
-      <c r="M9">
-        <v>9</v>
-      </c>
-      <c r="N9">
-        <v>9</v>
-      </c>
-      <c r="O9">
-        <v>8</v>
-      </c>
-      <c r="P9">
-        <v>8</v>
-      </c>
-      <c r="Q9">
-        <v>10</v>
-      </c>
-      <c r="R9">
-        <v>-1</v>
-      </c>
-      <c r="S9">
-        <v>-1</v>
-      </c>
-      <c r="T9">
-        <v>-1</v>
-      </c>
-      <c r="U9">
-        <v>-1</v>
-      </c>
-      <c r="V9">
-        <v>-1</v>
-      </c>
-      <c r="W9">
-        <v>-1</v>
-      </c>
-      <c r="X9">
-        <v>-1</v>
-      </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC9">
         <v>8</v>
       </c>
-      <c r="AD9">
-        <v>8</v>
-      </c>
-      <c r="AE9">
-        <v>7</v>
-      </c>
-      <c r="AF9">
-        <v>8</v>
-      </c>
-      <c r="AG9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33">
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -1403,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1415,19 +1327,19 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1445,13 +1357,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1460,27 +1372,15 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>5</v>
       </c>
-      <c r="AD10">
-        <v>5</v>
-      </c>
-      <c r="AE10">
-        <v>6</v>
-      </c>
-      <c r="AF10">
-        <v>5</v>
-      </c>
-      <c r="AG10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33">
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -1504,19 +1404,19 @@
         <v>5</v>
       </c>
       <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
         <v>10</v>
       </c>
-      <c r="J11">
-        <v>7</v>
-      </c>
-      <c r="K11">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>5</v>
-      </c>
       <c r="M11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>7</v>
@@ -1525,10 +1425,10 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q11">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1546,13 +1446,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1561,27 +1461,15 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>7</v>
-      </c>
-      <c r="AD11">
-        <v>7</v>
-      </c>
-      <c r="AE11">
-        <v>8</v>
-      </c>
-      <c r="AF11">
-        <v>6</v>
-      </c>
-      <c r="AG11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -1605,84 +1493,72 @@
         <v>5</v>
       </c>
       <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
+        <v>6</v>
+      </c>
+      <c r="L12">
+        <v>8</v>
+      </c>
+      <c r="M12">
+        <v>8</v>
+      </c>
+      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="O12">
+        <v>5</v>
+      </c>
+      <c r="P12">
+        <v>-1</v>
+      </c>
+      <c r="Q12">
+        <v>-1</v>
+      </c>
+      <c r="R12">
+        <v>-1</v>
+      </c>
+      <c r="S12">
+        <v>-1</v>
+      </c>
+      <c r="T12">
+        <v>-1</v>
+      </c>
+      <c r="U12">
+        <v>-1</v>
+      </c>
+      <c r="V12">
+        <v>-1</v>
+      </c>
+      <c r="W12">
+        <v>5</v>
+      </c>
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <v>6</v>
+      </c>
+      <c r="Z12">
+        <v>7</v>
+      </c>
+      <c r="AA12">
+        <v>8</v>
+      </c>
+      <c r="AB12">
         <v>10</v>
       </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>8</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-      <c r="M12">
-        <v>8</v>
-      </c>
-      <c r="N12">
-        <v>8</v>
-      </c>
-      <c r="O12">
-        <v>9</v>
-      </c>
-      <c r="P12">
-        <v>5</v>
-      </c>
-      <c r="Q12">
-        <v>10</v>
-      </c>
-      <c r="R12">
-        <v>-1</v>
-      </c>
-      <c r="S12">
-        <v>-1</v>
-      </c>
-      <c r="T12">
-        <v>-1</v>
-      </c>
-      <c r="U12">
-        <v>-1</v>
-      </c>
-      <c r="V12">
-        <v>-1</v>
-      </c>
-      <c r="W12">
-        <v>-1</v>
-      </c>
-      <c r="X12">
-        <v>-1</v>
-      </c>
-      <c r="Y12">
-        <v>-1</v>
-      </c>
-      <c r="Z12">
-        <v>5</v>
-      </c>
-      <c r="AA12">
-        <v>7</v>
-      </c>
-      <c r="AB12">
-        <v>6</v>
-      </c>
       <c r="AC12">
-        <v>7</v>
-      </c>
-      <c r="AD12">
-        <v>8</v>
-      </c>
-      <c r="AE12">
-        <v>10</v>
-      </c>
-      <c r="AF12">
-        <v>5</v>
-      </c>
-      <c r="AG12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1706,31 +1582,31 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Q13">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1748,42 +1624,30 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
-      </c>
-      <c r="AD13">
-        <v>9</v>
-      </c>
-      <c r="AE13">
-        <v>6</v>
-      </c>
-      <c r="AF13">
-        <v>7</v>
-      </c>
-      <c r="AG13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1807,31 +1671,31 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Q14">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1849,42 +1713,30 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>5</v>
-      </c>
-      <c r="AD14">
-        <v>8</v>
-      </c>
-      <c r="AE14">
-        <v>6</v>
-      </c>
-      <c r="AF14">
-        <v>7</v>
-      </c>
-      <c r="AG14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1908,84 +1760,72 @@
         <v>7</v>
       </c>
       <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>7</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
+        <v>8</v>
+      </c>
+      <c r="N15">
+        <v>9</v>
+      </c>
+      <c r="O15">
+        <v>8</v>
+      </c>
+      <c r="P15">
+        <v>-1</v>
+      </c>
+      <c r="Q15">
+        <v>-1</v>
+      </c>
+      <c r="R15">
+        <v>-1</v>
+      </c>
+      <c r="S15">
+        <v>-1</v>
+      </c>
+      <c r="T15">
+        <v>-1</v>
+      </c>
+      <c r="U15">
+        <v>-1</v>
+      </c>
+      <c r="V15">
+        <v>-1</v>
+      </c>
+      <c r="W15">
+        <v>7</v>
+      </c>
+      <c r="X15">
+        <v>7</v>
+      </c>
+      <c r="Y15">
+        <v>7</v>
+      </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15">
+        <v>8</v>
+      </c>
+      <c r="AB15">
         <v>10</v>
       </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-      <c r="K15">
-        <v>7</v>
-      </c>
-      <c r="L15">
-        <v>8</v>
-      </c>
-      <c r="M15">
-        <v>7</v>
-      </c>
-      <c r="N15">
-        <v>8</v>
-      </c>
-      <c r="O15">
-        <v>9</v>
-      </c>
-      <c r="P15">
-        <v>8</v>
-      </c>
-      <c r="Q15">
-        <v>10</v>
-      </c>
-      <c r="R15">
-        <v>-1</v>
-      </c>
-      <c r="S15">
-        <v>-1</v>
-      </c>
-      <c r="T15">
-        <v>-1</v>
-      </c>
-      <c r="U15">
-        <v>-1</v>
-      </c>
-      <c r="V15">
-        <v>-1</v>
-      </c>
-      <c r="W15">
-        <v>-1</v>
-      </c>
-      <c r="X15">
-        <v>-1</v>
-      </c>
-      <c r="Y15">
-        <v>-1</v>
-      </c>
-      <c r="Z15">
-        <v>7</v>
-      </c>
-      <c r="AA15">
-        <v>7</v>
-      </c>
-      <c r="AB15">
-        <v>7</v>
-      </c>
       <c r="AC15">
-        <v>5</v>
-      </c>
-      <c r="AD15">
-        <v>8</v>
-      </c>
-      <c r="AE15">
-        <v>10</v>
-      </c>
-      <c r="AF15">
-        <v>8</v>
-      </c>
-      <c r="AG15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -2009,84 +1849,72 @@
         <v>6</v>
       </c>
       <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>7</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>8</v>
+      </c>
+      <c r="M16">
+        <v>8</v>
+      </c>
+      <c r="N16">
+        <v>9</v>
+      </c>
+      <c r="O16">
+        <v>7</v>
+      </c>
+      <c r="P16">
+        <v>-1</v>
+      </c>
+      <c r="Q16">
+        <v>-1</v>
+      </c>
+      <c r="R16">
+        <v>-1</v>
+      </c>
+      <c r="S16">
+        <v>-1</v>
+      </c>
+      <c r="T16">
+        <v>-1</v>
+      </c>
+      <c r="U16">
+        <v>-1</v>
+      </c>
+      <c r="V16">
+        <v>-1</v>
+      </c>
+      <c r="W16">
+        <v>5</v>
+      </c>
+      <c r="X16">
+        <v>7</v>
+      </c>
+      <c r="Y16">
+        <v>5</v>
+      </c>
+      <c r="Z16">
+        <v>7</v>
+      </c>
+      <c r="AA16">
+        <v>8</v>
+      </c>
+      <c r="AB16">
         <v>10</v>
       </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <v>7</v>
-      </c>
-      <c r="L16">
-        <v>5</v>
-      </c>
-      <c r="M16">
-        <v>8</v>
-      </c>
-      <c r="N16">
-        <v>8</v>
-      </c>
-      <c r="O16">
-        <v>9</v>
-      </c>
-      <c r="P16">
-        <v>7</v>
-      </c>
-      <c r="Q16">
-        <v>10</v>
-      </c>
-      <c r="R16">
-        <v>-1</v>
-      </c>
-      <c r="S16">
-        <v>-1</v>
-      </c>
-      <c r="T16">
-        <v>-1</v>
-      </c>
-      <c r="U16">
-        <v>-1</v>
-      </c>
-      <c r="V16">
-        <v>-1</v>
-      </c>
-      <c r="W16">
-        <v>-1</v>
-      </c>
-      <c r="X16">
-        <v>-1</v>
-      </c>
-      <c r="Y16">
-        <v>-1</v>
-      </c>
-      <c r="Z16">
-        <v>5</v>
-      </c>
-      <c r="AA16">
-        <v>7</v>
-      </c>
-      <c r="AB16">
-        <v>5</v>
-      </c>
       <c r="AC16">
         <v>7</v>
       </c>
-      <c r="AD16">
-        <v>8</v>
-      </c>
-      <c r="AE16">
-        <v>10</v>
-      </c>
-      <c r="AF16">
-        <v>7</v>
-      </c>
-      <c r="AG16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -2110,13 +1938,13 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2125,16 +1953,16 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q17">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2152,42 +1980,30 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>5</v>
       </c>
-      <c r="AD17">
-        <v>5</v>
-      </c>
-      <c r="AE17">
-        <v>6</v>
-      </c>
-      <c r="AF17">
-        <v>5</v>
-      </c>
-      <c r="AG17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2211,13 +2027,13 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2226,16 +2042,16 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2253,42 +2069,30 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>5</v>
       </c>
-      <c r="AD18">
-        <v>5</v>
-      </c>
-      <c r="AE18">
-        <v>6</v>
-      </c>
-      <c r="AF18">
-        <v>5</v>
-      </c>
-      <c r="AG18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2312,31 +2116,31 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>7</v>
       </c>
       <c r="O19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q19">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2354,13 +2158,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2374,22 +2178,10 @@
       <c r="AC19">
         <v>5</v>
       </c>
-      <c r="AD19">
-        <v>7</v>
-      </c>
-      <c r="AE19">
-        <v>6</v>
-      </c>
-      <c r="AF19">
-        <v>5</v>
-      </c>
-      <c r="AG19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2413,31 +2205,31 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q20">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2455,13 +2247,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2470,27 +2262,15 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
       </c>
-      <c r="AD20">
-        <v>5</v>
-      </c>
-      <c r="AE20">
-        <v>6</v>
-      </c>
-      <c r="AF20">
-        <v>5</v>
-      </c>
-      <c r="AG20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33">
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -2514,84 +2294,72 @@
         <v>6</v>
       </c>
       <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>8</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>8</v>
+      </c>
+      <c r="N21">
+        <v>9</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21">
+        <v>-1</v>
+      </c>
+      <c r="Q21">
+        <v>-1</v>
+      </c>
+      <c r="R21">
+        <v>-1</v>
+      </c>
+      <c r="S21">
+        <v>-1</v>
+      </c>
+      <c r="T21">
+        <v>-1</v>
+      </c>
+      <c r="U21">
+        <v>-1</v>
+      </c>
+      <c r="V21">
+        <v>-1</v>
+      </c>
+      <c r="W21">
+        <v>6</v>
+      </c>
+      <c r="X21">
+        <v>7</v>
+      </c>
+      <c r="Y21">
+        <v>5</v>
+      </c>
+      <c r="Z21">
+        <v>5</v>
+      </c>
+      <c r="AA21">
+        <v>8</v>
+      </c>
+      <c r="AB21">
         <v>10</v>
       </c>
-      <c r="J21">
-        <v>5</v>
-      </c>
-      <c r="K21">
-        <v>8</v>
-      </c>
-      <c r="L21">
-        <v>4</v>
-      </c>
-      <c r="M21">
-        <v>5</v>
-      </c>
-      <c r="N21">
-        <v>8</v>
-      </c>
-      <c r="O21">
-        <v>9</v>
-      </c>
-      <c r="P21">
-        <v>5</v>
-      </c>
-      <c r="Q21">
-        <v>10</v>
-      </c>
-      <c r="R21">
-        <v>-1</v>
-      </c>
-      <c r="S21">
-        <v>-1</v>
-      </c>
-      <c r="T21">
-        <v>-1</v>
-      </c>
-      <c r="U21">
-        <v>-1</v>
-      </c>
-      <c r="V21">
-        <v>-1</v>
-      </c>
-      <c r="W21">
-        <v>-1</v>
-      </c>
-      <c r="X21">
-        <v>-1</v>
-      </c>
-      <c r="Y21">
-        <v>-1</v>
-      </c>
-      <c r="Z21">
-        <v>6</v>
-      </c>
-      <c r="AA21">
-        <v>7</v>
-      </c>
-      <c r="AB21">
-        <v>5</v>
-      </c>
       <c r="AC21">
         <v>5</v>
       </c>
-      <c r="AD21">
-        <v>8</v>
-      </c>
-      <c r="AE21">
-        <v>10</v>
-      </c>
-      <c r="AF21">
-        <v>5</v>
-      </c>
-      <c r="AG21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33">
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -2615,185 +2383,161 @@
         <v>8</v>
       </c>
       <c r="I22">
+        <v>8</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <v>9</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
         <v>10</v>
       </c>
-      <c r="J22">
-        <v>8</v>
-      </c>
-      <c r="K22">
-        <v>7</v>
-      </c>
-      <c r="L22">
-        <v>9</v>
-      </c>
-      <c r="M22">
-        <v>8</v>
-      </c>
       <c r="N22">
+        <v>7</v>
+      </c>
+      <c r="O22">
+        <v>8</v>
+      </c>
+      <c r="P22">
+        <v>-1</v>
+      </c>
+      <c r="Q22">
+        <v>-1</v>
+      </c>
+      <c r="R22">
+        <v>-1</v>
+      </c>
+      <c r="S22">
+        <v>-1</v>
+      </c>
+      <c r="T22">
+        <v>-1</v>
+      </c>
+      <c r="U22">
+        <v>-1</v>
+      </c>
+      <c r="V22">
+        <v>-1</v>
+      </c>
+      <c r="W22">
+        <v>7</v>
+      </c>
+      <c r="X22">
+        <v>8</v>
+      </c>
+      <c r="Y22">
+        <v>8</v>
+      </c>
+      <c r="Z22">
+        <v>7</v>
+      </c>
+      <c r="AA22">
         <v>10</v>
       </c>
-      <c r="O22">
-        <v>7</v>
-      </c>
-      <c r="P22">
-        <v>8</v>
-      </c>
-      <c r="Q22">
-        <v>10</v>
-      </c>
-      <c r="R22">
-        <v>-1</v>
-      </c>
-      <c r="S22">
-        <v>-1</v>
-      </c>
-      <c r="T22">
-        <v>-1</v>
-      </c>
-      <c r="U22">
-        <v>-1</v>
-      </c>
-      <c r="V22">
-        <v>-1</v>
-      </c>
-      <c r="W22">
-        <v>-1</v>
-      </c>
-      <c r="X22">
-        <v>-1</v>
-      </c>
-      <c r="Y22">
-        <v>-1</v>
-      </c>
-      <c r="Z22">
-        <v>7</v>
-      </c>
-      <c r="AA22">
-        <v>8</v>
-      </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>7</v>
-      </c>
-      <c r="AD22">
-        <v>10</v>
-      </c>
-      <c r="AE22">
-        <v>7</v>
-      </c>
-      <c r="AF22">
-        <v>8</v>
-      </c>
-      <c r="AG22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
+        <v>6</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>8</v>
+      </c>
+      <c r="N23">
+        <v>7</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+      <c r="P23">
+        <v>-1</v>
+      </c>
+      <c r="Q23">
+        <v>-1</v>
+      </c>
+      <c r="R23">
+        <v>-1</v>
+      </c>
+      <c r="S23">
+        <v>-1</v>
+      </c>
+      <c r="T23">
+        <v>-1</v>
+      </c>
+      <c r="U23">
+        <v>-1</v>
+      </c>
+      <c r="V23">
+        <v>-1</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="X23">
+        <v>8</v>
+      </c>
+      <c r="Y23">
+        <v>5</v>
+      </c>
+      <c r="Z23">
+        <v>5</v>
+      </c>
+      <c r="AA23">
+        <v>7</v>
+      </c>
+      <c r="AB23">
+        <v>7</v>
+      </c>
+      <c r="AC23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23">
-        <v>9</v>
-      </c>
-      <c r="D23">
-        <v>6</v>
-      </c>
-      <c r="E23">
-        <v>5</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23">
-        <v>7</v>
-      </c>
-      <c r="H23">
-        <v>5</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>5</v>
-      </c>
-      <c r="K23">
-        <v>6</v>
-      </c>
-      <c r="L23">
-        <v>4</v>
-      </c>
-      <c r="M23">
-        <v>5</v>
-      </c>
-      <c r="N23">
-        <v>8</v>
-      </c>
-      <c r="O23">
-        <v>7</v>
-      </c>
-      <c r="P23">
-        <v>6</v>
-      </c>
-      <c r="Q23">
-        <v>10</v>
-      </c>
-      <c r="R23">
-        <v>-1</v>
-      </c>
-      <c r="S23">
-        <v>-1</v>
-      </c>
-      <c r="T23">
-        <v>-1</v>
-      </c>
-      <c r="U23">
-        <v>-1</v>
-      </c>
-      <c r="V23">
-        <v>-1</v>
-      </c>
-      <c r="W23">
-        <v>-1</v>
-      </c>
-      <c r="X23">
-        <v>-1</v>
-      </c>
-      <c r="Y23">
-        <v>-1</v>
-      </c>
-      <c r="Z23">
-        <v>5</v>
-      </c>
-      <c r="AA23">
-        <v>8</v>
-      </c>
-      <c r="AB23">
-        <v>5</v>
-      </c>
-      <c r="AC23">
-        <v>5</v>
-      </c>
-      <c r="AD23">
-        <v>7</v>
-      </c>
-      <c r="AE23">
-        <v>7</v>
-      </c>
-      <c r="AF23">
-        <v>5</v>
-      </c>
-      <c r="AG23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -2817,31 +2561,31 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>9</v>
       </c>
       <c r="K24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>9</v>
       </c>
       <c r="N24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2859,42 +2603,30 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>7</v>
-      </c>
-      <c r="AD24">
-        <v>9</v>
-      </c>
-      <c r="AE24">
-        <v>7</v>
-      </c>
-      <c r="AF24">
-        <v>5</v>
-      </c>
-      <c r="AG24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -2918,84 +2650,72 @@
         <v>6</v>
       </c>
       <c r="I25">
+        <v>9</v>
+      </c>
+      <c r="J25">
+        <v>6</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25">
+        <v>8</v>
+      </c>
+      <c r="N25">
+        <v>9</v>
+      </c>
+      <c r="O25">
+        <v>9</v>
+      </c>
+      <c r="P25">
+        <v>-1</v>
+      </c>
+      <c r="Q25">
+        <v>-1</v>
+      </c>
+      <c r="R25">
+        <v>-1</v>
+      </c>
+      <c r="S25">
+        <v>-1</v>
+      </c>
+      <c r="T25">
+        <v>-1</v>
+      </c>
+      <c r="U25">
+        <v>-1</v>
+      </c>
+      <c r="V25">
+        <v>-1</v>
+      </c>
+      <c r="W25">
+        <v>9</v>
+      </c>
+      <c r="X25">
+        <v>7</v>
+      </c>
+      <c r="Y25">
+        <v>7</v>
+      </c>
+      <c r="Z25">
+        <v>9</v>
+      </c>
+      <c r="AA25">
+        <v>9</v>
+      </c>
+      <c r="AB25">
         <v>10</v>
       </c>
-      <c r="J25">
-        <v>9</v>
-      </c>
-      <c r="K25">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>6</v>
-      </c>
-      <c r="M25">
-        <v>8</v>
-      </c>
-      <c r="N25">
-        <v>8</v>
-      </c>
-      <c r="O25">
-        <v>9</v>
-      </c>
-      <c r="P25">
-        <v>9</v>
-      </c>
-      <c r="Q25">
-        <v>10</v>
-      </c>
-      <c r="R25">
-        <v>-1</v>
-      </c>
-      <c r="S25">
-        <v>-1</v>
-      </c>
-      <c r="T25">
-        <v>-1</v>
-      </c>
-      <c r="U25">
-        <v>-1</v>
-      </c>
-      <c r="V25">
-        <v>-1</v>
-      </c>
-      <c r="W25">
-        <v>-1</v>
-      </c>
-      <c r="X25">
-        <v>-1</v>
-      </c>
-      <c r="Y25">
-        <v>-1</v>
-      </c>
-      <c r="Z25">
-        <v>9</v>
-      </c>
-      <c r="AA25">
-        <v>7</v>
-      </c>
-      <c r="AB25">
-        <v>7</v>
-      </c>
       <c r="AC25">
-        <v>9</v>
-      </c>
-      <c r="AD25">
-        <v>9</v>
-      </c>
-      <c r="AE25">
-        <v>10</v>
-      </c>
-      <c r="AF25">
-        <v>8</v>
-      </c>
-      <c r="AG25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -3019,87 +2739,75 @@
         <v>8</v>
       </c>
       <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>8</v>
+      </c>
+      <c r="K26">
+        <v>9</v>
+      </c>
+      <c r="L26">
+        <v>7</v>
+      </c>
+      <c r="M26">
+        <v>9</v>
+      </c>
+      <c r="N26">
+        <v>7</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>-1</v>
+      </c>
+      <c r="Q26">
+        <v>-1</v>
+      </c>
+      <c r="R26">
+        <v>-1</v>
+      </c>
+      <c r="S26">
+        <v>-1</v>
+      </c>
+      <c r="T26">
+        <v>-1</v>
+      </c>
+      <c r="U26">
+        <v>-1</v>
+      </c>
+      <c r="V26">
+        <v>-1</v>
+      </c>
+      <c r="W26">
+        <v>7</v>
+      </c>
+      <c r="X26">
+        <v>9</v>
+      </c>
+      <c r="Y26">
+        <v>8</v>
+      </c>
+      <c r="Z26">
+        <v>7</v>
+      </c>
+      <c r="AA26">
         <v>10</v>
       </c>
-      <c r="J26">
-        <v>6</v>
-      </c>
-      <c r="K26">
-        <v>8</v>
-      </c>
-      <c r="L26">
-        <v>9</v>
-      </c>
-      <c r="M26">
-        <v>7</v>
-      </c>
-      <c r="N26">
-        <v>9</v>
-      </c>
-      <c r="O26">
-        <v>7</v>
-      </c>
-      <c r="P26">
-        <v>6</v>
-      </c>
-      <c r="Q26">
-        <v>10</v>
-      </c>
-      <c r="R26">
-        <v>-1</v>
-      </c>
-      <c r="S26">
-        <v>-1</v>
-      </c>
-      <c r="T26">
-        <v>-1</v>
-      </c>
-      <c r="U26">
-        <v>-1</v>
-      </c>
-      <c r="V26">
-        <v>-1</v>
-      </c>
-      <c r="W26">
-        <v>-1</v>
-      </c>
-      <c r="X26">
-        <v>-1</v>
-      </c>
-      <c r="Y26">
-        <v>-1</v>
-      </c>
-      <c r="Z26">
-        <v>7</v>
-      </c>
-      <c r="AA26">
-        <v>9</v>
-      </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>7</v>
-      </c>
-      <c r="AD26">
-        <v>10</v>
-      </c>
-      <c r="AE26">
-        <v>7</v>
-      </c>
-      <c r="AF26">
-        <v>7</v>
-      </c>
-      <c r="AG26">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="R1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="W1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3107,16 +2815,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3124,29 +2832,26 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25">
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3172,142 +2877,124 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>95</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>95</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4">
-        <v>95</v>
-      </c>
-      <c r="K4">
-        <v>100</v>
-      </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
-        <v>100</v>
-      </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
-        <v>95</v>
-      </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
-      <c r="U4">
-        <v>100</v>
-      </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-      <c r="W4">
-        <v>100</v>
-      </c>
-      <c r="X4">
-        <v>100</v>
-      </c>
-      <c r="Y4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B5">
         <v>90</v>
@@ -3331,60 +3018,51 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>95.5</v>
+      </c>
+      <c r="L5">
+        <v>87.5</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>90</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
-      <c r="L5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>95.5</v>
       </c>
-      <c r="M5">
+      <c r="S5">
         <v>87.5</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
         <v>90.59999999999999</v>
       </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
-        <v>90</v>
-      </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
-        <v>95.5</v>
-      </c>
-      <c r="U5">
-        <v>87.5</v>
-      </c>
       <c r="V5">
         <v>100</v>
       </c>
-      <c r="W5">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X5">
-        <v>100</v>
-      </c>
-      <c r="Y5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -3414,131 +3092,113 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>93.2</v>
       </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
         <v>96.90000000000001</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
-        <v>100</v>
-      </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>93.2</v>
-      </c>
-      <c r="U6">
-        <v>100</v>
-      </c>
       <c r="V6">
         <v>100</v>
       </c>
-      <c r="W6">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X6">
-        <v>100</v>
-      </c>
-      <c r="Y6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>97.7</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>97.7</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="L7">
-        <v>97.7</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
-      </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
-        <v>97.7</v>
-      </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-      <c r="W7">
-        <v>100</v>
-      </c>
-      <c r="X7">
-        <v>100</v>
-      </c>
-      <c r="Y7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -3562,137 +3222,119 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>93.2</v>
+      </c>
+      <c r="L8">
+        <v>87.5</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>81.3</v>
+      </c>
+      <c r="O8">
+        <v>87.5</v>
+      </c>
+      <c r="P8">
         <v>95</v>
       </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>93.2</v>
       </c>
-      <c r="M8">
+      <c r="S8">
         <v>87.5</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
         <v>81.3</v>
       </c>
-      <c r="P8">
+      <c r="V8">
         <v>87.5</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>95</v>
-      </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
-        <v>93.2</v>
-      </c>
-      <c r="U8">
-        <v>87.5</v>
-      </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-      <c r="W8">
-        <v>81.3</v>
-      </c>
-      <c r="X8">
-        <v>87.5</v>
-      </c>
-      <c r="Y8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>90</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-      <c r="K9">
-        <v>100</v>
-      </c>
-      <c r="L9">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
-        <v>90</v>
-      </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="U9">
-        <v>100</v>
-      </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
-      <c r="W9">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X9">
-        <v>100</v>
-      </c>
-      <c r="Y9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="B10">
         <v>70</v>
@@ -3716,60 +3358,51 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L10">
+        <v>81.3</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>68.8</v>
+      </c>
+      <c r="O10">
+        <v>75</v>
+      </c>
+      <c r="P10">
         <v>70</v>
       </c>
-      <c r="K10">
-        <v>100</v>
-      </c>
-      <c r="L10">
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>86.40000000000001</v>
       </c>
-      <c r="M10">
+      <c r="S10">
         <v>81.3</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
         <v>68.8</v>
       </c>
-      <c r="P10">
+      <c r="V10">
         <v>75</v>
       </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
-        <v>70</v>
-      </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="U10">
-        <v>81.3</v>
-      </c>
-      <c r="V10">
-        <v>100</v>
-      </c>
-      <c r="W10">
-        <v>68.8</v>
-      </c>
-      <c r="X10">
-        <v>75</v>
-      </c>
-      <c r="Y10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>80</v>
@@ -3793,40 +3426,40 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L11">
+        <v>93.8</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>93.8</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>80</v>
       </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
-      <c r="L11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>88.59999999999999</v>
       </c>
-      <c r="M11">
+      <c r="S11">
         <v>93.8</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>93.8</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
-        <v>80</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
       <c r="T11">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="U11">
         <v>93.8</v>
@@ -3834,19 +3467,10 @@
       <c r="V11">
         <v>100</v>
       </c>
-      <c r="W11">
-        <v>93.8</v>
-      </c>
-      <c r="X11">
-        <v>100</v>
-      </c>
-      <c r="Y11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -3870,60 +3494,51 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>93.2</v>
+      </c>
+      <c r="L12">
+        <v>87.5</v>
+      </c>
+      <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
         <v>75</v>
       </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>93.2</v>
       </c>
-      <c r="M12">
+      <c r="S12">
         <v>87.5</v>
       </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12">
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
         <v>90.59999999999999</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>75</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>93.2</v>
-      </c>
-      <c r="U12">
-        <v>87.5</v>
-      </c>
       <c r="V12">
         <v>100</v>
       </c>
-      <c r="W12">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X12">
-        <v>100</v>
-      </c>
-      <c r="Y12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>80</v>
@@ -3947,60 +3562,51 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L13">
+        <v>87.5</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>75</v>
       </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90.90000000000001</v>
       </c>
-      <c r="M13">
+      <c r="S13">
         <v>87.5</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
         <v>84.40000000000001</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>75</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U13">
-        <v>87.5</v>
-      </c>
       <c r="V13">
         <v>100</v>
       </c>
-      <c r="W13">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="X13">
-        <v>100</v>
-      </c>
-      <c r="Y13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4024,60 +3630,51 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L14">
+        <v>93.8</v>
+      </c>
+      <c r="M14">
+        <v>95.2</v>
+      </c>
+      <c r="N14">
+        <v>87.5</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
         <v>95</v>
       </c>
-      <c r="K14">
-        <v>100</v>
-      </c>
-      <c r="L14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>90.90000000000001</v>
       </c>
-      <c r="M14">
+      <c r="S14">
         <v>93.8</v>
       </c>
-      <c r="N14">
+      <c r="T14">
         <v>95.2</v>
       </c>
-      <c r="O14">
+      <c r="U14">
         <v>87.5</v>
       </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
-        <v>95</v>
-      </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-      <c r="T14">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U14">
-        <v>93.8</v>
-      </c>
       <c r="V14">
-        <v>95.2</v>
-      </c>
-      <c r="W14">
-        <v>87.5</v>
-      </c>
-      <c r="X14">
-        <v>100</v>
-      </c>
-      <c r="Y14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -4107,131 +3704,113 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>93.8</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>93.2</v>
       </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
         <v>93.8</v>
       </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>100</v>
-      </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-      <c r="T15">
-        <v>93.2</v>
-      </c>
-      <c r="U15">
-        <v>100</v>
-      </c>
       <c r="V15">
         <v>100</v>
       </c>
-      <c r="W15">
-        <v>93.8</v>
-      </c>
-      <c r="X15">
-        <v>100</v>
-      </c>
-      <c r="Y15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
+        <v>97.7</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>97.7</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="V16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
-      <c r="C16">
-        <v>100</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-      <c r="F16">
-        <v>100</v>
-      </c>
-      <c r="G16">
-        <v>100</v>
-      </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>97.7</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="P16">
-        <v>100</v>
-      </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>97.7</v>
-      </c>
-      <c r="U16">
-        <v>100</v>
-      </c>
-      <c r="V16">
-        <v>100</v>
-      </c>
-      <c r="W16">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X16">
-        <v>100</v>
-      </c>
-      <c r="Y16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -4255,60 +3834,51 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L17">
+        <v>87.5</v>
+      </c>
+      <c r="M17">
+        <v>90.5</v>
+      </c>
+      <c r="N17">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>90</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>84.09999999999999</v>
       </c>
-      <c r="M17">
+      <c r="S17">
         <v>87.5</v>
       </c>
-      <c r="N17">
+      <c r="T17">
         <v>90.5</v>
       </c>
-      <c r="O17">
+      <c r="U17">
         <v>90.59999999999999</v>
       </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>90</v>
-      </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="U17">
-        <v>87.5</v>
-      </c>
       <c r="V17">
-        <v>90.5</v>
-      </c>
-      <c r="W17">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X17">
-        <v>100</v>
-      </c>
-      <c r="Y17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>70</v>
@@ -4332,60 +3902,51 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L18">
+        <v>75</v>
+      </c>
+      <c r="M18">
+        <v>95.2</v>
+      </c>
+      <c r="N18">
+        <v>75</v>
+      </c>
+      <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>70</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>84.09999999999999</v>
       </c>
-      <c r="M18">
+      <c r="S18">
         <v>75</v>
       </c>
-      <c r="N18">
+      <c r="T18">
         <v>95.2</v>
-      </c>
-      <c r="O18">
-        <v>75</v>
-      </c>
-      <c r="P18">
-        <v>100</v>
-      </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>70</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>84.09999999999999</v>
       </c>
       <c r="U18">
         <v>75</v>
       </c>
       <c r="V18">
-        <v>95.2</v>
-      </c>
-      <c r="W18">
-        <v>75</v>
-      </c>
-      <c r="X18">
-        <v>100</v>
-      </c>
-      <c r="Y18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -4409,60 +3970,51 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L19">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="M19">
+        <v>95.2</v>
+      </c>
+      <c r="N19">
+        <v>81.3</v>
+      </c>
+      <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>85</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>86.40000000000001</v>
       </c>
-      <c r="M19">
+      <c r="S19">
         <v>71.90000000000001</v>
       </c>
-      <c r="N19">
+      <c r="T19">
         <v>95.2</v>
       </c>
-      <c r="O19">
+      <c r="U19">
         <v>81.3</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
-        <v>85</v>
-      </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="U19">
-        <v>71.90000000000001</v>
-      </c>
       <c r="V19">
-        <v>95.2</v>
-      </c>
-      <c r="W19">
-        <v>81.3</v>
-      </c>
-      <c r="X19">
-        <v>100</v>
-      </c>
-      <c r="Y19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -4486,60 +4038,51 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L20">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="M20">
+        <v>90.5</v>
+      </c>
+      <c r="N20">
+        <v>93.8</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
         <v>95</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>88.59999999999999</v>
       </c>
-      <c r="M20">
+      <c r="S20">
         <v>84.40000000000001</v>
       </c>
-      <c r="N20">
+      <c r="T20">
         <v>90.5</v>
       </c>
-      <c r="O20">
+      <c r="U20">
         <v>93.8</v>
       </c>
-      <c r="P20">
-        <v>100</v>
-      </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
-        <v>95</v>
-      </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="U20">
-        <v>84.40000000000001</v>
-      </c>
       <c r="V20">
-        <v>90.5</v>
-      </c>
-      <c r="W20">
-        <v>93.8</v>
-      </c>
-      <c r="X20">
-        <v>100</v>
-      </c>
-      <c r="Y20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -4563,60 +4106,51 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L21">
+        <v>75</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
         <v>80</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>86.40000000000001</v>
       </c>
-      <c r="M21">
+      <c r="S21">
         <v>75</v>
       </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
         <v>90.59999999999999</v>
       </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
-        <v>80</v>
-      </c>
-      <c r="S21">
-        <v>100</v>
-      </c>
-      <c r="T21">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="U21">
-        <v>75</v>
-      </c>
       <c r="V21">
         <v>100</v>
       </c>
-      <c r="W21">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X21">
-        <v>100</v>
-      </c>
-      <c r="Y21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>70</v>
@@ -4640,60 +4174,51 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
+        <v>93.8</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
         <v>85</v>
       </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
         <v>93.8</v>
       </c>
-      <c r="P22">
-        <v>100</v>
-      </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
-        <v>85</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
-        <v>100</v>
-      </c>
-      <c r="U22">
-        <v>100</v>
-      </c>
       <c r="V22">
         <v>100</v>
       </c>
-      <c r="W22">
-        <v>93.8</v>
-      </c>
-      <c r="X22">
-        <v>100</v>
-      </c>
-      <c r="Y22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -4723,54 +4248,45 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L23">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>90.90000000000001</v>
       </c>
-      <c r="M23">
+      <c r="S23">
         <v>90.59999999999999</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
         <v>84.40000000000001</v>
       </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>100</v>
-      </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U23">
-        <v>90.59999999999999</v>
-      </c>
       <c r="V23">
         <v>100</v>
       </c>
-      <c r="W23">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="X23">
-        <v>100</v>
-      </c>
-      <c r="Y23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -4800,131 +4316,113 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24">
+        <v>95.2</v>
+      </c>
+      <c r="N24">
+        <v>93.8</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>93.2</v>
       </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
-      <c r="N24">
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
         <v>95.2</v>
       </c>
-      <c r="O24">
+      <c r="U24">
         <v>93.8</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
-      <c r="T24">
-        <v>93.2</v>
-      </c>
-      <c r="U24">
-        <v>100</v>
-      </c>
       <c r="V24">
-        <v>95.2</v>
-      </c>
-      <c r="W24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>97.7</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
         <v>93.8</v>
       </c>
-      <c r="X24">
-        <v>100</v>
-      </c>
-      <c r="Y24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>97.7</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>93.8</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B25">
-        <v>100</v>
-      </c>
-      <c r="C25">
-        <v>100</v>
-      </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
-      <c r="E25">
-        <v>100</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
-      </c>
-      <c r="G25">
-        <v>100</v>
-      </c>
-      <c r="H25">
-        <v>100</v>
-      </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>97.7</v>
-      </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>93.8</v>
-      </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>100</v>
-      </c>
-      <c r="S25">
-        <v>100</v>
-      </c>
-      <c r="T25">
-        <v>97.7</v>
-      </c>
-      <c r="U25">
-        <v>100</v>
-      </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-      <c r="W25">
-        <v>93.8</v>
-      </c>
-      <c r="X25">
-        <v>100</v>
-      </c>
-      <c r="Y25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="B26">
         <v>90</v>
@@ -4948,37 +4446,37 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
         <v>90</v>
       </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
         <v>90.59999999999999</v>
-      </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
-        <v>90</v>
-      </c>
-      <c r="S26">
-        <v>100</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -4989,21 +4487,12 @@
       <c r="V26">
         <v>100</v>
       </c>
-      <c r="W26">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X26">
-        <v>100</v>
-      </c>
-      <c r="Y26">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5024,31 +4513,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5277,33 +4766,21 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>56</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
-        <v>100</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5338,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -5372,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -203,9 +203,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
@@ -218,7 +230,19 @@
     <t>NIETO</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
   </si>
   <si>
     <t>CAMACHO</t>
@@ -227,9 +251,6 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -237,6 +258,24 @@
   </si>
   <si>
     <t>ROSALES</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
   </si>
   <si>
     <t>IRVING JESUS</t>
@@ -4825,7 +4864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4857,16 +4896,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920256</v>
+        <v>24330051920274</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4880,22 +4919,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920256</v>
+        <v>24330051920274</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4903,16 +4942,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920266</v>
+        <v>24330051920274</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4926,16 +4965,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920266</v>
+        <v>24330051920274</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4949,16 +4988,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920257</v>
+        <v>24330051920267</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4972,16 +5011,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920257</v>
+        <v>24330051920267</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4995,22 +5034,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920279</v>
+        <v>24330051920267</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5018,22 +5057,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920311</v>
+        <v>24330051920267</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5041,24 +5080,507 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>24330051920369</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920369</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920369</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920369</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920255</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920255</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920255</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920390</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920390</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920390</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920262</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920262</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920262</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920256</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920256</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920266</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920266</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920257</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920257</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920279</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
         <v>24330051920270</v>
       </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F31" t="s">
         <v>52</v>
       </c>
-      <c r="G10">
+      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -167,27 +167,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -203,94 +203,106 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>NIETO</t>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PORRAS</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SALMERON</t>
-  </si>
-  <si>
     <t>ROSALES</t>
   </si>
   <si>
+    <t>JESUS DAMIAN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
     <t>BRYAN</t>
   </si>
   <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
     <t>ERNESTO</t>
   </si>
   <si>
-    <t>MARBELY YOSELIN</t>
+    <t>ALEXIS GABRIEL</t>
   </si>
   <si>
     <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL OSWALDO</t>
-  </si>
-  <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALISON</t>
   </si>
   <si>
     <t>MARTIN ERNESTO</t>
@@ -844,13 +856,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -865,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -933,13 +945,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -954,13 +966,13 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1022,13 +1034,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1046,10 +1058,10 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1111,13 +1123,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1132,7 +1144,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1200,13 +1212,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1221,13 +1233,13 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1289,13 +1301,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1313,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1378,13 +1390,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1399,13 +1411,13 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1467,13 +1479,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1494,7 +1506,7 @@
         <v>6</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1556,13 +1568,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1580,10 +1592,10 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -1645,13 +1657,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1669,10 +1681,10 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>9</v>
@@ -1734,13 +1746,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1758,10 +1770,10 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1823,13 +1835,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1850,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1885,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1912,13 +1924,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1936,10 +1948,10 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -1948,7 +1960,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2001,13 +2013,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2025,10 +2037,10 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2090,13 +2102,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2111,13 +2123,13 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -2179,13 +2191,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2206,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2268,13 +2280,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2289,13 +2301,13 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2357,13 +2369,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2381,10 +2393,10 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2446,13 +2458,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2470,10 +2482,10 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2535,13 +2547,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2556,13 +2568,13 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2624,13 +2636,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2645,7 +2657,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2713,13 +2725,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2734,10 +2746,10 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>9</v>
@@ -2802,13 +2814,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2823,7 +2835,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -3084,10 +3096,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95.5</v>
+        <v>87.5</v>
       </c>
       <c r="S5">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -3152,7 +3164,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3220,7 +3232,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3288,10 +3300,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>93.2</v>
+        <v>87.5</v>
       </c>
       <c r="S8">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3356,7 +3368,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3424,10 +3436,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S10">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -3492,10 +3504,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S11">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -3560,10 +3572,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S12">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -3628,10 +3640,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S13">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -3696,10 +3708,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S14">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T14">
         <v>95.2</v>
@@ -3764,7 +3776,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3832,7 +3844,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3900,10 +3912,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S17">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T17">
         <v>90.5</v>
@@ -3968,10 +3980,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S18">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="T18">
         <v>95.2</v>
@@ -4036,10 +4048,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S19">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="T19">
         <v>95.2</v>
@@ -4104,10 +4116,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S20">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T20">
         <v>90.5</v>
@@ -4172,10 +4184,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S21">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4240,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4308,10 +4320,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S23">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -4376,7 +4388,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4444,7 +4456,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4512,10 +4524,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -4581,7 +4593,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4590,19 +4602,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>43.5</v>
+        <v>47.8</v>
       </c>
       <c r="G2" s="2">
-        <v>56.5</v>
+        <v>52.2</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4613,7 +4625,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4622,19 +4634,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>43.5</v>
+        <v>52.2</v>
       </c>
       <c r="G3" s="2">
-        <v>56.5</v>
+        <v>47.8</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4645,7 +4657,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4654,19 +4666,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>47.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>52.2</v>
+        <v>17.4</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4677,7 +4689,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4686,19 +4698,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>52.2</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2">
-        <v>47.8</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4718,19 +4730,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4741,7 +4753,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -4750,19 +4762,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4773,7 +4785,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
@@ -4794,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4896,22 +4908,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920274</v>
+        <v>24330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4919,22 +4931,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920274</v>
+        <v>24330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4942,22 +4954,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920274</v>
+        <v>24330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4965,19 +4977,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920274</v>
+        <v>24330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
@@ -4988,22 +5000,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920267</v>
+        <v>24330051920407</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5011,22 +5023,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920267</v>
+        <v>24330051920407</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5034,19 +5046,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920267</v>
+        <v>24330051920407</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>50</v>
@@ -5057,22 +5069,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920267</v>
+        <v>24330051920409</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5080,19 +5092,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920369</v>
+        <v>24330051920409</v>
       </c>
       <c r="B10" t="s">
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>51</v>
@@ -5103,22 +5115,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920369</v>
+        <v>24330051920409</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5126,22 +5138,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920369</v>
+        <v>24330051920258</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5149,22 +5161,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920369</v>
+        <v>24330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5172,22 +5184,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920255</v>
+        <v>24330051920258</v>
       </c>
       <c r="B14" t="s">
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5195,19 +5207,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920255</v>
+        <v>24330051920405</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
@@ -5218,22 +5230,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920255</v>
+        <v>24330051920405</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5241,22 +5253,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920390</v>
+        <v>24330051920405</v>
       </c>
       <c r="B17" t="s">
         <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5264,22 +5276,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920390</v>
+        <v>24330051920369</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -5287,19 +5299,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920390</v>
+        <v>24330051920369</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>52</v>
@@ -5310,22 +5322,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920262</v>
+        <v>24330051920369</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -5333,22 +5345,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920262</v>
+        <v>24330051920267</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -5356,22 +5368,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920262</v>
+        <v>24330051920267</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -5382,19 +5394,19 @@
         <v>24330051920256</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -5405,19 +5417,19 @@
         <v>24330051920256</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -5425,19 +5437,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920266</v>
+        <v>24330051920390</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
@@ -5448,19 +5460,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920266</v>
+        <v>24330051920390</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>50</v>
@@ -5471,22 +5483,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920257</v>
+        <v>24330051920274</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -5494,19 +5506,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920257</v>
+        <v>24330051920255</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
         <v>49</v>
@@ -5517,19 +5529,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920279</v>
+        <v>24330051920257</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>49</v>
@@ -5540,19 +5552,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920311</v>
+        <v>24330051920262</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
         <v>50</v>
@@ -5566,19 +5578,19 @@
         <v>24330051920270</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G31">
         <v>5</v>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -173,18 +173,18 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
@@ -203,60 +203,60 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NIETO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>PANIAGUA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -266,31 +266,31 @@
     <t>ROSALES</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>JESUS DAMIAN</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
     <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>MARBELY YOSELIN</t>
   </si>
   <si>
     <t>BRYAN</t>
@@ -865,10 +865,10 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -954,10 +954,10 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1043,10 +1043,10 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1067,7 +1067,7 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1132,10 +1132,10 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1156,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1221,10 +1221,10 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1242,10 +1242,10 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1310,10 +1310,10 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1399,10 +1399,10 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1420,10 +1420,10 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1488,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1577,10 +1577,10 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1601,7 +1601,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1666,10 +1666,10 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1690,7 +1690,7 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1755,10 +1755,10 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1844,10 +1844,10 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1933,10 +1933,10 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1957,7 +1957,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -2022,10 +2022,10 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2043,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -2111,10 +2111,10 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2132,10 +2132,10 @@
         <v>6</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2200,10 +2200,10 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2289,10 +2289,10 @@
         <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2378,10 +2378,10 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2402,7 +2402,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2467,10 +2467,10 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2556,10 +2556,10 @@
         <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2645,10 +2645,10 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2734,10 +2734,10 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2758,7 +2758,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2823,10 +2823,10 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2844,10 +2844,10 @@
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -3105,7 +3105,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3173,7 +3173,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3309,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>81.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V8">
         <v>87.5</v>
@@ -3377,7 +3377,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3445,7 +3445,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>68.8</v>
+        <v>70.8</v>
       </c>
       <c r="V10">
         <v>75</v>
@@ -3581,7 +3581,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>90.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -3649,7 +3649,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -3714,10 +3714,10 @@
         <v>95.8</v>
       </c>
       <c r="T14">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U14">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -3785,7 +3785,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -3853,7 +3853,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -3918,10 +3918,10 @@
         <v>91.7</v>
       </c>
       <c r="T17">
-        <v>90.5</v>
+        <v>93.5</v>
       </c>
       <c r="U17">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -3986,10 +3986,10 @@
         <v>83.3</v>
       </c>
       <c r="T18">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U18">
-        <v>75</v>
+        <v>60.4</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4054,10 +4054,10 @@
         <v>81.3</v>
       </c>
       <c r="T19">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U19">
-        <v>81.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4122,10 +4122,10 @@
         <v>89.59999999999999</v>
       </c>
       <c r="T20">
-        <v>90.5</v>
+        <v>93.5</v>
       </c>
       <c r="U20">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4193,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4261,7 +4261,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4329,7 +4329,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4394,10 +4394,10 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4465,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4533,7 +4533,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4666,19 +4666,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>82.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="G4" s="2">
-        <v>17.4</v>
+        <v>21.7</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -4730,19 +4730,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4876,7 +4876,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4908,7 +4908,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920260</v>
+        <v>24330051920407</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920260</v>
+        <v>24330051920407</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920260</v>
+        <v>24330051920407</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4966,7 +4966,7 @@
         <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920260</v>
+        <v>24330051920407</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920407</v>
+        <v>24330051920260</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920407</v>
+        <v>24330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -5046,7 +5046,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920407</v>
+        <v>24330051920260</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -5058,10 +5058,10 @@
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920409</v>
+        <v>24330051920260</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5104,10 +5104,10 @@
         <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5127,10 +5127,10 @@
         <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5138,22 +5138,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920258</v>
+        <v>24330051920409</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920258</v>
+        <v>24330051920256</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
@@ -5173,10 +5173,10 @@
         <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920258</v>
+        <v>24330051920256</v>
       </c>
       <c r="B14" t="s">
         <v>64</v>
@@ -5196,10 +5196,10 @@
         <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5207,22 +5207,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920405</v>
+        <v>24330051920256</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5242,10 +5242,10 @@
         <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5265,10 +5265,10 @@
         <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5276,22 +5276,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920369</v>
+        <v>24330051920405</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -5299,22 +5299,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920369</v>
+        <v>24330051920390</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -5322,22 +5322,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920369</v>
+        <v>24330051920390</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920267</v>
+        <v>24330051920390</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -5368,22 +5368,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920267</v>
+        <v>24330051920369</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920256</v>
+        <v>24330051920369</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -5414,16 +5414,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920256</v>
+        <v>24330051920369</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -5437,16 +5437,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920390</v>
+        <v>24330051920267</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -5460,16 +5460,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920390</v>
+        <v>24330051920267</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -5483,16 +5483,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920274</v>
+        <v>24330051920258</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -5506,22 +5506,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920255</v>
+        <v>24330051920258</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -5529,16 +5529,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920257</v>
+        <v>24330051920274</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920262</v>
+        <v>24330051920255</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -5575,24 +5575,70 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
+        <v>24330051920257</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920262</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
         <v>24330051920270</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>66</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
         <v>81</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>95</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>50</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -221,15 +221,15 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -251,21 +251,15 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>CHACON</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -287,25 +281,19 @@
     <t>JESUS ENRIQUE</t>
   </si>
   <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
     <t>GABRIEL URYEL</t>
   </si>
   <si>
-    <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>BRYAN</t>
-  </si>
-  <si>
     <t>ERNESTO</t>
   </si>
   <si>
     <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
   </si>
 </sst>
 </file>
@@ -871,7 +859,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -960,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -981,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1049,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1070,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1138,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1227,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1316,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1405,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1494,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1583,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1672,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1761,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1850,7 +1838,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1871,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1939,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1960,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2028,7 +2016,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2117,7 +2105,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2206,7 +2194,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2295,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2384,7 +2372,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2405,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2473,7 +2461,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2562,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2651,7 +2639,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2672,7 +2660,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2740,7 +2728,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2761,7 +2749,7 @@
         <v>9</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2829,7 +2817,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -3312,7 +3300,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="V8">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3448,7 +3436,7 @@
         <v>70.8</v>
       </c>
       <c r="V10">
-        <v>75</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3584,7 +3572,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3924,7 +3912,7 @@
         <v>93.8</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3992,7 +3980,7 @@
         <v>60.4</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4060,7 +4048,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="V19">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4128,7 +4116,7 @@
         <v>95.8</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4332,7 +4320,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4634,19 +4622,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>52.2</v>
+        <v>65.2</v>
       </c>
       <c r="G3" s="2">
-        <v>47.8</v>
+        <v>34.8</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4876,7 +4864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4917,7 +4905,7 @@
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4940,7 +4928,7 @@
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4963,7 +4951,7 @@
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4986,7 +4974,7 @@
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -5009,7 +4997,7 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5032,7 +5020,7 @@
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5055,7 +5043,7 @@
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5078,7 +5066,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -5101,7 +5089,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5124,7 +5112,7 @@
         <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5147,7 +5135,7 @@
         <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -5170,7 +5158,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -5193,7 +5181,7 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5216,7 +5204,7 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -5239,7 +5227,7 @@
         <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5262,7 +5250,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5285,7 +5273,7 @@
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -5308,7 +5296,7 @@
         <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -5331,7 +5319,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -5354,7 +5342,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -5377,7 +5365,7 @@
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -5400,7 +5388,7 @@
         <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -5423,7 +5411,7 @@
         <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -5437,7 +5425,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920267</v>
+        <v>24330051920258</v>
       </c>
       <c r="B25" t="s">
         <v>67</v>
@@ -5446,7 +5434,7 @@
         <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -5460,7 +5448,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920267</v>
+        <v>24330051920258</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -5469,7 +5457,7 @@
         <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -5483,7 +5471,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920258</v>
+        <v>24330051920274</v>
       </c>
       <c r="B27" t="s">
         <v>68</v>
@@ -5492,7 +5480,7 @@
         <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -5506,22 +5494,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920258</v>
+        <v>24330051920267</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -5529,16 +5517,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920274</v>
+        <v>24330051920255</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -5552,16 +5540,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920255</v>
+        <v>24330051920257</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -5570,75 +5558,6 @@
         <v>49</v>
       </c>
       <c r="G30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>24330051920257</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>24330051920262</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>24330051920270</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20241.xlsx
+++ b/grupos/1DV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -230,7 +230,7 @@
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>PAZ</t>
+    <t>MOTA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -260,6 +260,9 @@
     <t>CHACON</t>
   </si>
   <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -293,7 +296,7 @@
     <t>ERNESTO</t>
   </si>
   <si>
-    <t>ALEXIS GABRIEL</t>
+    <t>ANGEL OSWALDO</t>
   </si>
 </sst>
 </file>
@@ -841,7 +844,7 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -862,7 +865,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -930,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1019,7 +1022,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1108,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1129,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1197,7 +1200,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1286,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1375,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1464,7 +1467,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1553,7 +1556,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1642,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1731,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1752,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1820,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1841,7 +1844,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1909,7 +1912,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1930,7 +1933,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1998,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -2087,7 +2090,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -2176,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2265,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2354,7 +2357,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2375,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2443,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2464,7 +2467,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2532,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2621,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>7</v>
@@ -2642,7 +2645,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2710,7 +2713,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -2799,7 +2802,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2820,7 +2823,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -3010,7 +3013,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3078,7 +3081,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>81.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3146,7 +3149,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3282,7 +3285,7 @@
         <v>87.5</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3350,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3418,7 +3421,7 @@
         <v>75</v>
       </c>
       <c r="P10">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3486,7 +3489,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3554,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3622,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3690,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3894,7 +3897,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3962,7 +3965,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4030,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>85</v>
+        <v>81.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4098,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4166,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4234,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4506,7 +4509,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4602,7 +4605,7 @@
         <v>52.2</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4905,7 +4908,7 @@
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4928,7 +4931,7 @@
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4951,7 +4954,7 @@
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4974,7 +4977,7 @@
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -4997,7 +5000,7 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5020,7 +5023,7 @@
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5043,7 +5046,7 @@
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5066,7 +5069,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -5089,7 +5092,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5112,7 +5115,7 @@
         <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5135,7 +5138,7 @@
         <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -5158,7 +5161,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -5181,7 +5184,7 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5204,7 +5207,7 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -5227,7 +5230,7 @@
         <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5250,7 +5253,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5273,7 +5276,7 @@
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -5296,7 +5299,7 @@
         <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -5319,7 +5322,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -5342,7 +5345,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -5365,7 +5368,7 @@
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -5388,7 +5391,7 @@
         <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -5411,7 +5414,7 @@
         <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -5434,7 +5437,7 @@
         <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -5457,7 +5460,7 @@
         <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -5480,7 +5483,7 @@
         <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -5503,7 +5506,7 @@
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -5526,7 +5529,7 @@
         <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -5540,16 +5543,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920257</v>
+        <v>24330051920266</v>
       </c>
       <c r="B30" t="s">
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
